--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486765_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486765_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1617</v>
+        <v>6.093</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3612</v>
+        <v>3.9133</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8005</v>
+        <v>2.1797</v>
       </c>
       <c r="G2" t="n">
         <v>2.358</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8962</v>
+        <v>0.8275</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9302</v>
+        <v>0.4823</v>
       </c>
       <c r="U2" t="n">
-        <v>0.966</v>
+        <v>0.3452</v>
       </c>
       <c r="V2" t="n">
         <v>1.5559</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0503</v>
+        <v>5.4116</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2132</v>
+        <v>4.4752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8371</v>
+        <v>0.9364</v>
       </c>
       <c r="G3" t="n">
         <v>6.7785</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0718</v>
+        <v>0.2896</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1373</v>
+        <v>0.3993</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2091</v>
+        <v>-0.1098</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2703</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7654</v>
+        <v>4.7972</v>
       </c>
       <c r="E4" t="n">
-        <v>2.229</v>
+        <v>2.2359</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5364</v>
+        <v>2.5612</v>
       </c>
       <c r="G4" t="n">
         <v>5.3021</v>
@@ -766,13 +766,13 @@
         <v>3.6685</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1543</v>
+        <v>0.1861</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0063</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1549</v>
+        <v>0.1798</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2703</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. DIOP</t>
+          <t>A. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5093</v>
+        <v>3.1955</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.4179</v>
+        <v>1.1691</v>
       </c>
       <c r="F5" t="n">
-        <v>4.9272</v>
+        <v>2.0264</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5181</v>
+        <v>2.1236</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7999000000000001</v>
+        <v>1.4409</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.318</v>
+        <v>0.6827</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4343</v>
+        <v>2.7869</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.096</v>
+        <v>2.1313</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3383</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9162</v>
+        <v>-0.6634</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8959</v>
+        <v>-0.6904</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0203</v>
+        <v>0.0271</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3515</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>-3.0892</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3169</v>
+        <v>2.51</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.1378</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3038</v>
+        <v>-0.0419</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3811</v>
+        <v>0.1797</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5985</v>
+        <v>1.5133</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X5" t="n">
-        <v>1.3129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GUERRA LOZANO</t>
+          <t>P. DIOP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8329</v>
+        <v>2.5148</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07969999999999999</v>
+        <v>-2.3627</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7532</v>
+        <v>4.8775</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1236</v>
+        <v>-0.5181</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4409</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6827</v>
+        <v>-1.318</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7869</v>
+        <v>-1.4343</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1313</v>
+        <v>-0.096</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6556999999999999</v>
+        <v>-1.3383</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6634</v>
+        <v>0.9162</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6904</v>
+        <v>0.8959</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0271</v>
+        <v>0.0203</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0892</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>2.51</v>
+        <v>2.3169</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2247</v>
+        <v>0.0828</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1313</v>
+        <v>-0.2486</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0935</v>
+        <v>0.3314</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5133</v>
+        <v>1.5985</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5133</v>
+        <v>0.2856</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.3129</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9622000000000001</v>
+        <v>1.5097</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0033</v>
+        <v>-2.431</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9656</v>
+        <v>3.9407</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2733</v>
@@ -1000,13 +1000,13 @@
         <v>3.2823</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7612</v>
+        <v>-0.2138</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0209</v>
+        <v>-0.4486</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2597</v>
+        <v>0.2349</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2856</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8233</v>
+        <v>0.9515</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0483</v>
+        <v>0.0551</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8716</v>
+        <v>0.8964</v>
       </c>
       <c r="G8" t="n">
         <v>0.3379</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.0344</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4935</v>
+        <v>0.2825</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4274</v>
+        <v>0.1172</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1654</v>
       </c>
       <c r="G9" t="n">
         <v>0.0412</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6453</v>
+        <v>0.4344</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.2688</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.1655</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6672</v>
+        <v>-1.0423</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8757</v>
+        <v>-4.0273</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2085</v>
+        <v>2.985</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9482</v>
@@ -1234,13 +1234,13 @@
         <v>3.6685</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8716</v>
+        <v>0.4964</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3305</v>
+        <v>0.1788</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5411</v>
+        <v>0.3176</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3282</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7076</v>
+        <v>-3.0924</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8373</v>
+        <v>-2.5201</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8703</v>
+        <v>-0.5723</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1898</v>
@@ -1312,13 +1312,13 @@
         <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2981</v>
+        <v>0.3171</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2211</v>
+        <v>0.0961</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.077</v>
+        <v>0.221</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7989</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9235</v>
+        <v>-5.769</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7032</v>
+        <v>-3.6481</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2203</v>
+        <v>-2.121</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0448</v>
@@ -1390,13 +1390,13 @@
         <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7005</v>
+        <v>0.855</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2204</v>
+        <v>0.2756</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4801</v>
+        <v>0.5795</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0692</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3003</v>
+        <v>14.8521</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5752</v>
+        <v>-3.023399999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>17.8756</v>
+        <v>17.8754</v>
       </c>
       <c r="G13" t="n">
         <v>8.9671</v>
@@ -1438,10 +1438,10 @@
         <v>4.830299999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1369</v>
+        <v>4.136900000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>8.081</v>
+        <v>8.081000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>5.526099999999999</v>
@@ -1450,7 +1450,7 @@
         <v>2.5549</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8860000000000001</v>
+        <v>0.8860000000000006</v>
       </c>
       <c r="N13" t="n">
         <v>-0.6957</v>
@@ -1468,19 +1468,19 @@
         <v>23.1692</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8956</v>
+        <v>3.4473</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4094000000000002</v>
+        <v>0.9611999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4861</v>
+        <v>2.4862</v>
       </c>
       <c r="V13" t="n">
         <v>-3.3548</v>
       </c>
       <c r="W13" t="n">
-        <v>5.311500000000001</v>
+        <v>5.3115</v>
       </c>
       <c r="X13" t="n">
         <v>-8.666399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3232</v>
+        <v>3.0238</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1962</v>
+        <v>1.6099</v>
       </c>
       <c r="F14" t="n">
-        <v>1.127</v>
+        <v>1.4139</v>
       </c>
       <c r="G14" t="n">
         <v>1.603</v>
@@ -1546,13 +1546,13 @@
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5074</v>
+        <v>0.1931</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1107</v>
+        <v>0.303</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3967</v>
+        <v>-0.1098</v>
       </c>
       <c r="V14" t="n">
         <v>1.2277</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. PIZARRO</t>
+          <t>M. VILLANUEVA CUBELO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.738</v>
+        <v>1.7208</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7673</v>
+        <v>-1.374</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0292</v>
+        <v>3.0948</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4246</v>
+        <v>-0.2795</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5241</v>
+        <v>0.5999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09950000000000001</v>
+        <v>-0.8794</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3554</v>
+        <v>-0.2982</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.317</v>
+        <v>0.8773</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0384</v>
+        <v>-1.1755</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0692</v>
+        <v>0.0187</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2071</v>
+        <v>-0.2774</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1379</v>
+        <v>0.2961</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9654</v>
+        <v>2.8962</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.4551</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5515</v>
+        <v>-0.635</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6398</v>
+        <v>0.1799</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2856</v>
+        <v>2.4554</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5712</v>
+        <v>2.4554</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VILLANUEVA CUBELO</t>
+          <t>J. FERMIN DE LUNA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3831</v>
+        <v>1.1852</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2014</v>
+        <v>-0.4531</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5845</v>
+        <v>1.6383</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2795</v>
+        <v>1.4348</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5999</v>
+        <v>1.3308</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8794</v>
+        <v>0.104</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2982</v>
+        <v>1.9674</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8773</v>
+        <v>1.8838</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1755</v>
+        <v>0.0837</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0187</v>
+        <v>-0.5327</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2774</v>
+        <v>-0.553</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2961</v>
+        <v>0.0203</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8962</v>
+        <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7928</v>
+        <v>-0.2689</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4624</v>
+        <v>-0.7521</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3304</v>
+        <v>0.4832</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4554</v>
+        <v>0.9847</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4554</v>
+        <v>1.2277</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. FERMIN DE LUNA</t>
+          <t>M. PIZARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3067</v>
+        <v>0.3989</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9702</v>
+        <v>0.3536</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2769</v>
+        <v>0.0453</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4348</v>
+        <v>-0.4246</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3308</v>
+        <v>-0.5241</v>
       </c>
       <c r="I17" t="n">
-        <v>0.104</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9674</v>
+        <v>-0.3554</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8838</v>
+        <v>-0.317</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0837</v>
+        <v>-0.0384</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5327</v>
+        <v>-0.0692</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.553</v>
+        <v>-0.2071</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0203</v>
+        <v>0.1379</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9654</v>
+        <v>0.9654</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1474</v>
+        <v>-0.4275</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2692</v>
+        <v>0.1378</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1218</v>
+        <v>-0.5653</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9847</v>
+        <v>0.2856</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>0.5712</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.243</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7048</v>
+        <v>-0.3738</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7872</v>
+        <v>-0.5804</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0824</v>
+        <v>0.2066</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9255</v>
@@ -1858,13 +1858,13 @@
         <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9378</v>
+        <v>-0.6068</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1932</v>
+        <v>0.0136</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7446</v>
+        <v>-0.6204</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0687</v>
+        <v>-1.563</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5003</v>
+        <v>-0.7417</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4316</v>
+        <v>-0.8214</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.854</v>
+        <v>-0.508</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.3032</v>
+        <v>-1.0212</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4492</v>
+        <v>0.5132</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.7764</v>
+        <v>1.2651</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.3364</v>
+        <v>0.0828</v>
       </c>
       <c r="L19" t="n">
-        <v>1.56</v>
+        <v>1.1824</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0777</v>
+        <v>-1.7731</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9668</v>
+        <v>-1.1039</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1108</v>
+        <v>-0.6692</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.0892</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.7923</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7031</v>
+        <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4771</v>
+        <v>-0.0896</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1576</v>
+        <v>-0.076</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3194</v>
+        <v>-0.0136</v>
       </c>
       <c r="V19" t="n">
-        <v>3.3975</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.9108</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9478</v>
+        <v>-3.1526</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0519</v>
+        <v>-4.0516</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8959</v>
+        <v>0.899</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.508</v>
+        <v>-3.854</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0212</v>
+        <v>-5.3032</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5132</v>
+        <v>1.4492</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2651</v>
+        <v>-2.7764</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0828</v>
+        <v>-4.3364</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1824</v>
+        <v>1.56</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7731</v>
+        <v>-1.0777</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1039</v>
+        <v>-0.9668</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6692</v>
+        <v>-0.1108</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9654</v>
+        <v>-3.0892</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-5.7923</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9654</v>
+        <v>2.7031</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4744</v>
+        <v>0.3932</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3863</v>
+        <v>-0.3937</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0881</v>
+        <v>0.7869</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3.3975</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>4.9108</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. BERGERON</t>
+          <t>J. HERNÁNDEZ TRUJILLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2619</v>
+        <v>-3.6351</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9308</v>
+        <v>-3.8176</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3311</v>
+        <v>0.1824</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6302</v>
+        <v>-1.3692</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5996</v>
+        <v>-0.4559</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2298</v>
+        <v>-0.9133</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0335</v>
+        <v>-0.3612</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6009</v>
+        <v>0.1655</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5674</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6637</v>
+        <v>-1.008</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0012</v>
+        <v>-0.6214</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6624</v>
+        <v>-0.3866</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8317</v>
+        <v>-0.1654</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6889</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1428</v>
+        <v>-0.2616</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.498</v>
+        <v>-0.9421</v>
       </c>
       <c r="W21" t="n">
-        <v>0.243</v>
+        <v>-0.6565</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.741</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. HERNÁNDEZ TRUJILLO</t>
+          <t>G. BERGERON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3687</v>
+        <v>-3.8383</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4381</v>
+        <v>-2.8616</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0694</v>
+        <v>-0.9767</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3692</v>
+        <v>-0.6302</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4559</v>
+        <v>0.5996</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9133</v>
+        <v>-1.2298</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3612</v>
+        <v>0.0335</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1655</v>
+        <v>0.6009</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5674</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.008</v>
+        <v>-0.6637</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6214</v>
+        <v>-0.0012</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3866</v>
+        <v>-0.6624</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.899</v>
+        <v>0.2553</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5243</v>
+        <v>-0.2419</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3747</v>
+        <v>0.4972</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9421</v>
+        <v>-2.498</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6565</v>
+        <v>0.243</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2856</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.6993</v>
+        <v>-7.3764</v>
       </c>
       <c r="E23" t="n">
         <v>-5.9588</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7404</v>
+        <v>-1.4176</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0138</v>
@@ -2248,13 +2248,13 @@
         <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3572</v>
+        <v>-1.0344</v>
       </c>
       <c r="T23" t="n">
         <v>-0.9381</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4191</v>
+        <v>-0.0963</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5559</v>
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.3002</v>
+        <v>-13.6105</v>
       </c>
       <c r="E24" t="n">
-        <v>-17.8752</v>
+        <v>-17.8753</v>
       </c>
       <c r="F24" t="n">
-        <v>3.5752</v>
+        <v>4.2646</v>
       </c>
       <c r="G24" t="n">
-        <v>-8.966999999999999</v>
+        <v>-8.967000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.830300000000001</v>
+        <v>-4.8303</v>
       </c>
       <c r="I24" t="n">
         <v>-4.136699999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8861999999999999</v>
+        <v>-0.8862000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6958999999999995</v>
+        <v>0.6958999999999991</v>
       </c>
       <c r="L24" t="n">
         <v>-1.5818</v>
@@ -2326,22 +2326,22 @@
         <v>17.3772</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.8956</v>
+        <v>-2.2061</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.486200000000001</v>
+        <v>-2.4862</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4094000000000001</v>
+        <v>0.2802000000000002</v>
       </c>
       <c r="V24" t="n">
         <v>3.3549</v>
       </c>
       <c r="W24" t="n">
-        <v>8.666300000000001</v>
+        <v>8.6663</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.3115</v>
+        <v>-5.311500000000001</v>
       </c>
     </row>
   </sheetData>
